--- a/Result/profitability/4558.xlsx
+++ b/Result/profitability/4558.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM39"/>
+  <dimension ref="A1:AM40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5383,6 +5383,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4558</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>582</v>
+      </c>
+      <c r="D40" t="n">
+        <v>519</v>
+      </c>
+      <c r="E40" t="n">
+        <v>63</v>
+      </c>
+      <c r="F40" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="G40" t="n">
+        <v>32</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5.52%</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J40" t="n">
+        <v>29</v>
+      </c>
+      <c r="K40" t="n">
+        <v>22</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-0.01500000000000001</v>
+      </c>
+      <c r="N40" t="n">
+        <v>6.51375</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X40" t="n">
+        <v>6.333333333333334</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>-0.4000000000000004</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-0.035810205908684</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>-1.977777777777778</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>-6.279411764705882</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK40" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
